--- a/Bibsam_tidskriftslistor/scifree_data_spie.xlsx
+++ b/Bibsam_tidskriftslistor/scifree_data_spie.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_B9A55E9327DD001F3236A4FD2727587BCA2802A4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DBD4D1E7-C1B0-4DCA-BEF7-BF620272AC7B}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -180,9 +181,6 @@
     <t>Journal of Optical Microsystems</t>
   </si>
   <si>
-    <t>Photonics Insights</t>
-  </si>
-  <si>
     <t>https://www.spiedigitallibrary.org/journals/advanced-photonics-nexus</t>
   </si>
   <si>
@@ -195,16 +193,19 @@
     <t>2708-5260</t>
   </si>
   <si>
-    <t>https://www.spiedigitallibrary.org/journals/photonics-insights</t>
-  </si>
-  <si>
-    <t>2791-1748</t>
+    <t>3005-4745</t>
+  </si>
+  <si>
+    <t>Biophotonics Discovery</t>
+  </si>
+  <si>
+    <t>https://www.spiedigitallibrary.org/journals/biophotonics-discovery</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -292,19 +293,19 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G15" totalsRowShown="0" headerRowDxfId="0">
-  <autoFilter ref="A1:G15"/>
-  <sortState ref="A2:G15">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:G15" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="A1:G15" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G15">
     <sortCondition ref="D1:D15"/>
   </sortState>
   <tableColumns count="7">
-    <tableColumn id="1" name="Imprint"/>
-    <tableColumn id="2" name="ISSN Electronic"/>
-    <tableColumn id="3" name="ISSN Print"/>
-    <tableColumn id="4" name="Journal Name"/>
-    <tableColumn id="5" name="JournalURL"/>
-    <tableColumn id="6" name="Publishing model"/>
-    <tableColumn id="7" name="CC License options"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Imprint"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="ISSN Electronic"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="ISSN Print"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Journal Name"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="JournalURL"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Publishing model"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="CC License options"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -572,7 +573,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -633,13 +634,13 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D3" t="s">
         <v>51</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F3" t="s">
         <v>0</v>
@@ -652,17 +653,17 @@
       <c r="A4" t="s">
         <v>8</v>
       </c>
-      <c r="C4" t="s">
-        <v>12</v>
+      <c r="B4" t="s">
+        <v>57</v>
       </c>
       <c r="D4" t="s">
-        <v>13</v>
+        <v>58</v>
       </c>
       <c r="E4" t="s">
-        <v>14</v>
+        <v>59</v>
       </c>
       <c r="F4" t="s">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="G4" t="s">
         <v>50</v>
@@ -672,17 +673,14 @@
       <c r="A5" t="s">
         <v>8</v>
       </c>
-      <c r="B5" t="s">
-        <v>15</v>
-      </c>
       <c r="C5" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D5" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E5" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F5" t="s">
         <v>49</v>
@@ -696,19 +694,19 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D6" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F6" t="s">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="G6" t="s">
         <v>50</v>
@@ -719,19 +717,19 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D7" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E7" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F7" t="s">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="G7" t="s">
         <v>50</v>
@@ -742,16 +740,16 @@
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C8" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D8" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E8" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F8" t="s">
         <v>49</v>
@@ -765,16 +763,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D9" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E9" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F9" t="s">
         <v>49</v>
@@ -787,14 +785,17 @@
       <c r="A10" t="s">
         <v>8</v>
       </c>
+      <c r="B10" t="s">
+        <v>31</v>
+      </c>
       <c r="C10" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D10" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E10" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="F10" t="s">
         <v>49</v>
@@ -807,17 +808,17 @@
       <c r="A11" t="s">
         <v>8</v>
       </c>
-      <c r="B11" t="s">
-        <v>57</v>
+      <c r="C11" t="s">
+        <v>35</v>
       </c>
       <c r="D11" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="E11" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="F11" t="s">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="G11" t="s">
         <v>50</v>
@@ -828,16 +829,16 @@
         <v>8</v>
       </c>
       <c r="B12" t="s">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="D12" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="E12" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="F12" t="s">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="G12" t="s">
         <v>50</v>
@@ -848,19 +849,16 @@
         <v>8</v>
       </c>
       <c r="B13" t="s">
-        <v>41</v>
-      </c>
-      <c r="C13" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D13" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E13" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F13" t="s">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="G13" t="s">
         <v>50</v>
@@ -871,19 +869,19 @@
         <v>8</v>
       </c>
       <c r="B14" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C14" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D14" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E14" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F14" t="s">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="G14" t="s">
         <v>50</v>
@@ -894,16 +892,19 @@
         <v>8</v>
       </c>
       <c r="B15" t="s">
-        <v>59</v>
+        <v>45</v>
+      </c>
+      <c r="C15" t="s">
+        <v>46</v>
       </c>
       <c r="D15" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="E15" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="F15" t="s">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="G15" t="s">
         <v>50</v>
@@ -911,7 +912,7 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="E3" r:id="rId1"/>
+    <hyperlink ref="E3" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>

--- a/Bibsam_tidskriftslistor/scifree_data_spie.xlsx
+++ b/Bibsam_tidskriftslistor/scifree_data_spie.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="3" documentId="11_B9A55E9327DD001F3236A4FD2727587BCA2802A4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DBD4D1E7-C1B0-4DCA-BEF7-BF620272AC7B}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31538ED0-220C-44D1-A828-1F0DAFCAA105}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -115,18 +115,9 @@
     <t>https://www.spiedigitallibrary.org/journals/journal-of-medical-imaging</t>
   </si>
   <si>
-    <t>1932-5134</t>
-  </si>
-  <si>
     <t>1932-5150</t>
   </si>
   <si>
-    <t xml:space="preserve">Journal of Micro/Nanolithography, MEMS and MOEMS </t>
-  </si>
-  <si>
-    <t>https://www.spiedigitallibrary.org/journals/journal-of-micro-nanolithography-mems-and-moems</t>
-  </si>
-  <si>
     <t>1934-2608</t>
   </si>
   <si>
@@ -200,32 +191,25 @@
   </si>
   <si>
     <t>https://www.spiedigitallibrary.org/journals/biophotonics-discovery</t>
+  </si>
+  <si>
+    <t>2708-8340</t>
+  </si>
+  <si>
+    <t>Journal of Micro/Nanopatterning, Materials, and Metrology</t>
+  </si>
+  <si>
+    <t>https://www.spiedigitallibrary.org/journals/journal-of-micro-nanopatterning-materials-and-metrology</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -248,38 +232,16 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -293,19 +255,16 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:G15" totalsRowShown="0" headerRowDxfId="0">
-  <autoFilter ref="A1:G15" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G15">
-    <sortCondition ref="D1:D15"/>
-  </sortState>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{4FFC8206-4ECF-4587-950A-C1F401C13912}" name="Table2" displayName="Table2" ref="A1:G15" totalsRowShown="0">
+  <autoFilter ref="A1:G15" xr:uid="{4FFC8206-4ECF-4587-950A-C1F401C13912}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Imprint"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="ISSN Electronic"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="ISSN Print"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Journal Name"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="JournalURL"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Publishing model"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="CC License options"/>
+    <tableColumn id="1" xr3:uid="{D929F62B-A78D-473D-804A-D5770FDF38C4}" name="Imprint"/>
+    <tableColumn id="2" xr3:uid="{EB0F99BA-2B6D-4DB8-ADCE-29D85DC6D1ED}" name="ISSN Electronic"/>
+    <tableColumn id="3" xr3:uid="{BDB4ED52-177C-4B78-B7A8-9DC51B2424B6}" name="ISSN Print"/>
+    <tableColumn id="4" xr3:uid="{0BABD844-3C89-48AB-832A-9B42168F6804}" name="Journal Name"/>
+    <tableColumn id="5" xr3:uid="{A32E1332-E037-4C44-8517-B2A86F79FAE3}" name="JournalURL"/>
+    <tableColumn id="6" xr3:uid="{7B3E4CD1-D861-4498-BCEB-8F1858AF3EFE}" name="Publishing model"/>
+    <tableColumn id="7" xr3:uid="{B1CB7F64-943C-45A6-8D0C-0236B517F7BA}" name="CC License options"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -573,39 +532,39 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC6C35CD-7E5C-47C9-9874-B35C8CF03015}">
   <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" customWidth="1"/>
-    <col min="2" max="2" width="19.140625" customWidth="1"/>
-    <col min="3" max="3" width="16.5703125" customWidth="1"/>
-    <col min="4" max="4" width="57.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="25.5703125" customWidth="1"/>
+    <col min="2" max="2" width="16.28515625" customWidth="1"/>
+    <col min="3" max="3" width="11.85546875" customWidth="1"/>
+    <col min="4" max="4" width="15.28515625" customWidth="1"/>
+    <col min="5" max="5" width="12.85546875" customWidth="1"/>
     <col min="6" max="6" width="18.5703125" customWidth="1"/>
     <col min="7" max="7" width="19.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
     </row>
@@ -626,7 +585,7 @@
         <v>0</v>
       </c>
       <c r="G2" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -634,19 +593,19 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D3" t="s">
-        <v>51</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>53</v>
+        <v>48</v>
+      </c>
+      <c r="E3" t="s">
+        <v>50</v>
       </c>
       <c r="F3" t="s">
         <v>0</v>
       </c>
       <c r="G3" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -654,19 +613,19 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D4" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E4" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="F4" t="s">
         <v>0</v>
       </c>
       <c r="G4" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -683,10 +642,10 @@
         <v>14</v>
       </c>
       <c r="F5" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G5" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -706,10 +665,10 @@
         <v>18</v>
       </c>
       <c r="F6" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G6" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -732,7 +691,7 @@
         <v>0</v>
       </c>
       <c r="G7" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -752,10 +711,10 @@
         <v>26</v>
       </c>
       <c r="F8" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G8" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -775,10 +734,10 @@
         <v>30</v>
       </c>
       <c r="F9" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G9" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -786,22 +745,22 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
+        <v>57</v>
+      </c>
+      <c r="C10" t="s">
         <v>31</v>
       </c>
-      <c r="C10" t="s">
-        <v>32</v>
-      </c>
       <c r="D10" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="E10" t="s">
-        <v>34</v>
+        <v>59</v>
       </c>
       <c r="F10" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G10" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -809,19 +768,19 @@
         <v>8</v>
       </c>
       <c r="C11" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D11" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E11" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="F11" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G11" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -829,19 +788,19 @@
         <v>8</v>
       </c>
       <c r="B12" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D12" t="s">
+        <v>49</v>
+      </c>
+      <c r="E12" t="s">
         <v>52</v>
-      </c>
-      <c r="E12" t="s">
-        <v>55</v>
       </c>
       <c r="F12" t="s">
         <v>0</v>
       </c>
       <c r="G12" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -849,19 +808,19 @@
         <v>8</v>
       </c>
       <c r="B13" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D13" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E13" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="F13" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G13" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -869,22 +828,22 @@
         <v>8</v>
       </c>
       <c r="B14" t="s">
+        <v>38</v>
+      </c>
+      <c r="C14" t="s">
+        <v>39</v>
+      </c>
+      <c r="D14" t="s">
+        <v>40</v>
+      </c>
+      <c r="E14" t="s">
         <v>41</v>
-      </c>
-      <c r="C14" t="s">
-        <v>42</v>
-      </c>
-      <c r="D14" t="s">
-        <v>43</v>
-      </c>
-      <c r="E14" t="s">
-        <v>44</v>
       </c>
       <c r="F14" t="s">
         <v>0</v>
       </c>
       <c r="G14" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -892,32 +851,28 @@
         <v>8</v>
       </c>
       <c r="B15" t="s">
+        <v>42</v>
+      </c>
+      <c r="C15" t="s">
+        <v>43</v>
+      </c>
+      <c r="D15" t="s">
+        <v>44</v>
+      </c>
+      <c r="E15" t="s">
         <v>45</v>
       </c>
-      <c r="C15" t="s">
+      <c r="F15" t="s">
         <v>46</v>
       </c>
-      <c r="D15" t="s">
-        <v>47</v>
-      </c>
-      <c r="E15" t="s">
-        <v>48</v>
-      </c>
-      <c r="F15" t="s">
-        <v>49</v>
-      </c>
       <c r="G15" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="E3" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
   <tableParts count="1">
-    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>